--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_MOVISTAR ESTUDIANTES.xlsx
@@ -565,13 +565,13 @@
         <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>65.718</v>
+        <v>77.0774</v>
       </c>
       <c r="E2" t="n">
-        <v>50.71579999999999</v>
+        <v>58.0881</v>
       </c>
       <c r="F2" t="n">
-        <v>15.002</v>
+        <v>18.9893</v>
       </c>
       <c r="G2" t="n">
         <v>69.69930000000001</v>
@@ -610,13 +610,13 @@
         <v>47.6338</v>
       </c>
       <c r="S2" t="n">
-        <v>-11.3356</v>
+        <v>0.02400000000000002</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.4283</v>
+        <v>-2.0556</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.9073</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>16.2713</v>
@@ -643,13 +643,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>27.9747</v>
+        <v>41.4487</v>
       </c>
       <c r="E3" t="n">
-        <v>31.0824</v>
+        <v>37.8205</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.107600000000001</v>
+        <v>3.6283</v>
       </c>
       <c r="G3" t="n">
         <v>15.4178</v>
@@ -688,13 +688,13 @@
         <v>49.5912</v>
       </c>
       <c r="S3" t="n">
-        <v>-14.7653</v>
+        <v>-1.2919</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.209</v>
+        <v>-4.4714</v>
       </c>
       <c r="U3" t="n">
-        <v>-3.5563</v>
+        <v>3.1793</v>
       </c>
       <c r="V3" t="n">
         <v>6.2249</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>21.3011</v>
+        <v>36.821</v>
       </c>
       <c r="E4" t="n">
-        <v>25.6087</v>
+        <v>37.7331</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.3079</v>
+        <v>-0.9122999999999997</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7966</v>
+        <v>19.4203</v>
       </c>
       <c r="H4" t="n">
-        <v>20.1257</v>
+        <v>11.0368</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.329899999999999</v>
+        <v>8.3835</v>
       </c>
       <c r="J4" t="n">
-        <v>45.4888</v>
+        <v>50.1603</v>
       </c>
       <c r="K4" t="n">
-        <v>28.4193</v>
+        <v>16.5492</v>
       </c>
       <c r="L4" t="n">
-        <v>17.0693</v>
+        <v>33.6111</v>
       </c>
       <c r="M4" t="n">
-        <v>-32.6923</v>
+        <v>-30.74</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.2934</v>
+        <v>-5.5125</v>
       </c>
       <c r="O4" t="n">
-        <v>-24.3989</v>
+        <v>-25.2275</v>
       </c>
       <c r="P4" t="n">
-        <v>7.1777</v>
+        <v>-8.265000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-39.1508</v>
+        <v>-43.9363</v>
       </c>
       <c r="R4" t="n">
-        <v>46.3287</v>
+        <v>35.6709</v>
       </c>
       <c r="S4" t="n">
-        <v>11.7116</v>
+        <v>-2.9431</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2654</v>
+        <v>-3.9723</v>
       </c>
       <c r="U4" t="n">
-        <v>8.4465</v>
+        <v>1.0294</v>
       </c>
       <c r="V4" t="n">
-        <v>-10.385</v>
+        <v>28.6091</v>
       </c>
       <c r="W4" t="n">
-        <v>16.0056</v>
+        <v>35.4817</v>
       </c>
       <c r="X4" t="n">
-        <v>-26.3909</v>
+        <v>-6.8726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>20.4399</v>
+        <v>18.3293</v>
       </c>
       <c r="E5" t="n">
-        <v>27.1883</v>
+        <v>23.017</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.7484</v>
+        <v>-4.6876</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4203</v>
+        <v>12.7966</v>
       </c>
       <c r="H5" t="n">
-        <v>11.0368</v>
+        <v>20.1257</v>
       </c>
       <c r="I5" t="n">
-        <v>8.3835</v>
+        <v>-7.329899999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>50.1603</v>
+        <v>45.4888</v>
       </c>
       <c r="K5" t="n">
-        <v>16.5492</v>
+        <v>28.4193</v>
       </c>
       <c r="L5" t="n">
-        <v>33.6111</v>
+        <v>17.0693</v>
       </c>
       <c r="M5" t="n">
-        <v>-30.74</v>
+        <v>-32.6923</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.5125</v>
+        <v>-8.2934</v>
       </c>
       <c r="O5" t="n">
-        <v>-25.2275</v>
+        <v>-24.3989</v>
       </c>
       <c r="P5" t="n">
-        <v>-8.265000000000001</v>
+        <v>7.1777</v>
       </c>
       <c r="Q5" t="n">
-        <v>-43.9363</v>
+        <v>-39.1508</v>
       </c>
       <c r="R5" t="n">
-        <v>35.6709</v>
+        <v>46.3287</v>
       </c>
       <c r="S5" t="n">
-        <v>-19.3243</v>
+        <v>8.7403</v>
       </c>
       <c r="T5" t="n">
-        <v>-14.5174</v>
+        <v>0.6731999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.8068</v>
+        <v>8.066800000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>28.6091</v>
+        <v>-10.385</v>
       </c>
       <c r="W5" t="n">
-        <v>35.4817</v>
+        <v>16.0056</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.8726</v>
+        <v>-26.3909</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>11.5367</v>
+        <v>9.182600000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>21.4561</v>
+        <v>10.2258</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.9201</v>
+        <v>-1.043099999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2184</v>
+        <v>-2.585400000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>13.3521</v>
+        <v>-2.2847</v>
       </c>
       <c r="I6" t="n">
-        <v>-8.133700000000001</v>
+        <v>-0.3003000000000007</v>
       </c>
       <c r="J6" t="n">
-        <v>23.9219</v>
+        <v>19.1833</v>
       </c>
       <c r="K6" t="n">
-        <v>20.0571</v>
+        <v>5.139799999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8643</v>
+        <v>14.0434</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.7034</v>
+        <v>-21.7685</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.7051</v>
+        <v>-7.4245</v>
       </c>
       <c r="O6" t="n">
-        <v>-11.9988</v>
+        <v>-14.3442</v>
       </c>
       <c r="P6" t="n">
-        <v>-14.5733</v>
+        <v>12.8328</v>
       </c>
       <c r="Q6" t="n">
-        <v>-47.8513</v>
+        <v>-22.6204</v>
       </c>
       <c r="R6" t="n">
-        <v>33.2782</v>
+        <v>35.4532</v>
       </c>
       <c r="S6" t="n">
-        <v>15.621</v>
+        <v>-1.979</v>
       </c>
       <c r="T6" t="n">
-        <v>11.3212</v>
+        <v>-5.0434</v>
       </c>
       <c r="U6" t="n">
-        <v>4.2995</v>
+        <v>3.0643</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2699</v>
+        <v>0.9141000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>34.0647</v>
+        <v>18.7068</v>
       </c>
       <c r="X6" t="n">
-        <v>-28.7945</v>
+        <v>-17.7926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>10.4052</v>
+        <v>6.617100000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>11.3384</v>
+        <v>3.0357</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9332000000000001</v>
+        <v>3.581399999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-11.0033</v>
+        <v>1.654599999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6898</v>
+        <v>3.579</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.313</v>
+        <v>-1.9244</v>
       </c>
       <c r="J7" t="n">
-        <v>7.615600000000001</v>
+        <v>6.1265</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9109</v>
+        <v>5.382</v>
       </c>
       <c r="L7" t="n">
-        <v>4.7041</v>
+        <v>0.7444000000000002</v>
       </c>
       <c r="M7" t="n">
-        <v>-18.6188</v>
+        <v>-4.4719</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.600999999999999</v>
+        <v>-1.803</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.0178</v>
+        <v>-2.669</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.175</v>
+        <v>4.7851</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.4906</v>
+        <v>-11.9627</v>
       </c>
       <c r="R7" t="n">
-        <v>21.3153</v>
+        <v>16.748</v>
       </c>
       <c r="S7" t="n">
-        <v>17.2448</v>
+        <v>-0.5622</v>
       </c>
       <c r="T7" t="n">
-        <v>12.2044</v>
+        <v>0.1816</v>
       </c>
       <c r="U7" t="n">
-        <v>5.0404</v>
+        <v>-0.7435</v>
       </c>
       <c r="V7" t="n">
-        <v>6.3384</v>
+        <v>0.7394000000000004</v>
       </c>
       <c r="W7" t="n">
-        <v>15.0089</v>
+        <v>8.690799999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.670399999999999</v>
+        <v>-7.951099999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>8.820499999999999</v>
+        <v>4.853300000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>5.715300000000001</v>
+        <v>4.7687</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1052</v>
+        <v>0.08439999999999986</v>
       </c>
       <c r="G8" t="n">
-        <v>9.377600000000001</v>
+        <v>1.8112</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6549</v>
+        <v>12.3275</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7226</v>
+        <v>-10.5162</v>
       </c>
       <c r="J8" t="n">
-        <v>8.5379</v>
+        <v>19.405</v>
       </c>
       <c r="K8" t="n">
-        <v>4.713</v>
+        <v>20.079</v>
       </c>
       <c r="L8" t="n">
-        <v>3.8247</v>
+        <v>-0.6740999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8394999999999998</v>
+        <v>-17.5937</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9421</v>
+        <v>-7.7515</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1024</v>
+        <v>-9.8424</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5225</v>
+        <v>-9.5701</v>
       </c>
       <c r="Q8" t="n">
-        <v>-12.6152</v>
+        <v>-31.321</v>
       </c>
       <c r="R8" t="n">
-        <v>11.0925</v>
+        <v>21.7504</v>
       </c>
       <c r="S8" t="n">
-        <v>15.1517</v>
+        <v>4.4351</v>
       </c>
       <c r="T8" t="n">
-        <v>10.2541</v>
+        <v>1.8712</v>
       </c>
       <c r="U8" t="n">
-        <v>4.897399999999999</v>
+        <v>2.564</v>
       </c>
       <c r="V8" t="n">
-        <v>-14.1862</v>
+        <v>8.177199999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4616</v>
+        <v>14.8138</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.7248</v>
+        <v>-6.6365</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>7.907100000000001</v>
+        <v>3.382000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>7.3248</v>
+        <v>12.9523</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5822000000000001</v>
+        <v>-9.5702</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8112</v>
+        <v>5.2184</v>
       </c>
       <c r="H9" t="n">
-        <v>12.3275</v>
+        <v>13.3521</v>
       </c>
       <c r="I9" t="n">
-        <v>-10.5162</v>
+        <v>-8.133700000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>19.405</v>
+        <v>23.9219</v>
       </c>
       <c r="K9" t="n">
-        <v>20.079</v>
+        <v>20.0571</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6740999999999999</v>
+        <v>3.8643</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.5937</v>
+        <v>-18.7034</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.7515</v>
+        <v>-6.7051</v>
       </c>
       <c r="O9" t="n">
-        <v>-9.8424</v>
+        <v>-11.9988</v>
       </c>
       <c r="P9" t="n">
-        <v>-9.5701</v>
+        <v>-14.5733</v>
       </c>
       <c r="Q9" t="n">
-        <v>-31.321</v>
+        <v>-47.8513</v>
       </c>
       <c r="R9" t="n">
-        <v>21.7504</v>
+        <v>33.2782</v>
       </c>
       <c r="S9" t="n">
-        <v>7.4889</v>
+        <v>7.4665</v>
       </c>
       <c r="T9" t="n">
-        <v>4.4274</v>
+        <v>2.817</v>
       </c>
       <c r="U9" t="n">
-        <v>3.0618</v>
+        <v>4.6495</v>
       </c>
       <c r="V9" t="n">
-        <v>8.177199999999999</v>
+        <v>5.2699</v>
       </c>
       <c r="W9" t="n">
-        <v>14.8138</v>
+        <v>34.0647</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.6365</v>
+        <v>-28.7945</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D10" t="n">
-        <v>5.3686</v>
+        <v>0.5281999999999996</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1777</v>
+        <v>3.633999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1907</v>
+        <v>-3.1065</v>
       </c>
       <c r="G10" t="n">
-        <v>1.654599999999999</v>
+        <v>-11.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>3.579</v>
+        <v>-3.6898</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9244</v>
+        <v>-7.313</v>
       </c>
       <c r="J10" t="n">
-        <v>6.1265</v>
+        <v>7.615600000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>5.382</v>
+        <v>2.9109</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7444000000000002</v>
+        <v>4.7041</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.4719</v>
+        <v>-18.6188</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.803</v>
+        <v>-6.600999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.669</v>
+        <v>-12.0178</v>
       </c>
       <c r="P10" t="n">
-        <v>4.7851</v>
+        <v>-2.175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.9627</v>
+        <v>-23.4906</v>
       </c>
       <c r="R10" t="n">
-        <v>16.748</v>
+        <v>21.3153</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8107</v>
+        <v>7.3678</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6765999999999999</v>
+        <v>4.500599999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1342</v>
+        <v>2.8674</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7394000000000004</v>
+        <v>6.3384</v>
       </c>
       <c r="W10" t="n">
-        <v>8.690799999999999</v>
+        <v>15.0089</v>
       </c>
       <c r="X10" t="n">
-        <v>-7.951099999999999</v>
+        <v>-8.670399999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4226</v>
+        <v>0.0663</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2907</v>
+        <v>0.3967</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1319</v>
+        <v>-0.3304</v>
       </c>
       <c r="G11" t="n">
         <v>0.2836</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1612</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6188</v>
+        <v>0.7247</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5426000000000001</v>
+        <v>0.08019999999999994</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3697999999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7237999999999998</v>
+        <v>-0.9242000000000006</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5567</v>
+        <v>-1.4304</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.833</v>
+        <v>0.5059000000000005</v>
       </c>
       <c r="G12" t="n">
-        <v>4.553599999999999</v>
+        <v>9.377600000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7536</v>
+        <v>7.6549</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2000000000000001</v>
+        <v>1.7226</v>
       </c>
       <c r="J12" t="n">
-        <v>6.476</v>
+        <v>8.5379</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9404</v>
+        <v>4.713</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5354</v>
+        <v>3.8247</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9226</v>
+        <v>0.8394999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.187</v>
+        <v>2.9421</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7356</v>
+        <v>-2.1024</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.6102</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.6552</v>
+        <v>-12.6152</v>
       </c>
       <c r="R12" t="n">
-        <v>3.045</v>
+        <v>11.0925</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7147</v>
+        <v>5.4072</v>
       </c>
       <c r="T12" t="n">
-        <v>2.085</v>
+        <v>3.1089</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6297</v>
+        <v>2.2982</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.9342</v>
+        <v>-14.1862</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3491</v>
+        <v>-0.4616</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.585199999999999</v>
+        <v>-13.7248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9961</v>
+        <v>-1.1135</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3927</v>
+        <v>0.5702000000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6034</v>
+        <v>-1.6839</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0828</v>
+        <v>4.553599999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3163</v>
+        <v>4.7536</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2335</v>
+        <v>-0.2000000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0182</v>
+        <v>6.476</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0182</v>
+        <v>5.9404</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.5354</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0645</v>
+        <v>-1.9226</v>
       </c>
       <c r="N13" t="n">
-        <v>0.298</v>
+        <v>-1.187</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2335</v>
+        <v>-0.7356</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.0875</v>
+        <v>-2.6102</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>-5.6552</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.045</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3991</v>
+        <v>0.8772</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6766</v>
+        <v>0.0986999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2775</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3904</v>
+        <v>-3.9342</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3904</v>
+        <v>-3.585199999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.370900000000001</v>
+        <v>-1.3006</v>
       </c>
       <c r="E14" t="n">
-        <v>2.362800000000001</v>
+        <v>-0.728</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.7342</v>
+        <v>-0.5726</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.585400000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.2847</v>
+        <v>0.3163</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3003000000000007</v>
+        <v>-0.2335</v>
       </c>
       <c r="J14" t="n">
-        <v>19.1833</v>
+        <v>0.0182</v>
       </c>
       <c r="K14" t="n">
-        <v>5.139799999999999</v>
+        <v>0.0182</v>
       </c>
       <c r="L14" t="n">
-        <v>14.0434</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.7685</v>
+        <v>0.0645</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.4245</v>
+        <v>0.298</v>
       </c>
       <c r="O14" t="n">
-        <v>-14.3442</v>
+        <v>-0.2335</v>
       </c>
       <c r="P14" t="n">
-        <v>12.8328</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.6204</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>35.4532</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-14.5325</v>
+        <v>0.0946</v>
       </c>
       <c r="T14" t="n">
-        <v>-12.9062</v>
+        <v>0.3413</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6265</v>
+        <v>-0.2466</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9141000000000001</v>
+        <v>-0.3904</v>
       </c>
       <c r="W14" t="n">
-        <v>18.7068</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.7926</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>-3.8008</v>
+        <v>-1.434200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8039000000000001</v>
+        <v>1.4741</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.604699999999999</v>
+        <v>-2.908200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2847999999999999</v>
+        <v>16.8567</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1581</v>
+        <v>6.1077</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1267</v>
+        <v>10.7491</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3179</v>
+        <v>35.0856</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9194</v>
+        <v>11.5485</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3985</v>
+        <v>23.5372</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0331</v>
+        <v>-18.2293</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7613</v>
+        <v>-5.440900000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2718</v>
+        <v>-12.7884</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.4349999999999999</v>
+        <v>-18.2706</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>-47.1988</v>
       </c>
       <c r="R15" t="n">
-        <v>1.74</v>
+        <v>28.9282</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1953</v>
+        <v>1.3357</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3389</v>
+        <v>-1.1437</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8563999999999999</v>
+        <v>2.4794</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.4551</v>
+        <v>-1.3559</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>14.731</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4551</v>
+        <v>-16.0872</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.1187</v>
+        <v>-3.1765</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.9451</v>
+        <v>1.0274</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1731</v>
+        <v>-4.204</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2092</v>
+        <v>0.2847999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9188</v>
+        <v>0.1581</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2901</v>
+        <v>0.1267</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7394999999999999</v>
+        <v>3.3179</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.1437</v>
+        <v>1.9194</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4039</v>
+        <v>1.3985</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4697</v>
+        <v>-3.0331</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2243</v>
+        <v>-1.7613</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6944</v>
+        <v>-1.2718</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.2174999999999997</v>
+        <v>-0.4349999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.48</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2625</v>
+        <v>1.74</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1717</v>
+        <v>-0.5710999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7259</v>
+        <v>-0.1153</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4458999999999999</v>
+        <v>-0.4557</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.5204</v>
+        <v>-2.4551</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.5204</v>
+        <v>-2.4551</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.6501</v>
+        <v>-4.5721</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.073399999999999</v>
+        <v>-4.4296</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.5762</v>
+        <v>-0.1424</v>
       </c>
       <c r="G17" t="n">
-        <v>16.8567</v>
+        <v>-2.2092</v>
       </c>
       <c r="H17" t="n">
-        <v>6.1077</v>
+        <v>-0.9188</v>
       </c>
       <c r="I17" t="n">
-        <v>10.7491</v>
+        <v>-1.2901</v>
       </c>
       <c r="J17" t="n">
-        <v>35.0856</v>
+        <v>-0.7394999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>11.5485</v>
+        <v>-1.1437</v>
       </c>
       <c r="L17" t="n">
-        <v>23.5372</v>
+        <v>0.4039</v>
       </c>
       <c r="M17" t="n">
-        <v>-18.2293</v>
+        <v>-1.4697</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.440900000000001</v>
+        <v>0.2243</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.7884</v>
+        <v>-1.6944</v>
       </c>
       <c r="P17" t="n">
-        <v>-18.2706</v>
+        <v>-0.2174999999999997</v>
       </c>
       <c r="Q17" t="n">
-        <v>-47.1988</v>
+        <v>-3.48</v>
       </c>
       <c r="R17" t="n">
-        <v>28.9282</v>
+        <v>3.2625</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.88</v>
+        <v>-0.6251</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.6914</v>
+        <v>-0.2103</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8113</v>
+        <v>-0.4147000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.3559</v>
+        <v>-1.5204</v>
       </c>
       <c r="W17" t="n">
-        <v>14.731</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-16.0872</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.7422</v>
+        <v>-6.0989</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.4071</v>
+        <v>-7.0466</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6648999999999997</v>
+        <v>0.9477999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3163</v>
@@ -1858,13 +1858,13 @@
         <v>8.2651</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.09790000000000004</v>
+        <v>0.5453000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.799</v>
+        <v>-1.4383</v>
       </c>
       <c r="U18" t="n">
-        <v>1.7009</v>
+        <v>1.9837</v>
       </c>
       <c r="V18" t="n">
         <v>-1.3251</v>
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.308199999999999</v>
+        <v>-6.4527</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.589700000000001</v>
+        <v>-2.6901</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.718500000000001</v>
+        <v>-3.7629</v>
       </c>
       <c r="G19" t="n">
         <v>0.1519000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>5.22</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.658</v>
+        <v>0.1973</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.7654</v>
+        <v>0.1345999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8929</v>
+        <v>0.06269999999999998</v>
       </c>
       <c r="V19" t="n">
         <v>-6.5846</v>
@@ -1969,13 +1969,13 @@
         <v>32</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.451799999999999</v>
+        <v>-8.511700000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>17.171</v>
+        <v>13.9081</v>
       </c>
       <c r="F20" t="n">
-        <v>-26.623</v>
+        <v>-22.4205</v>
       </c>
       <c r="G20" t="n">
         <v>-1.436599999999999</v>
@@ -2014,13 +2014,13 @@
         <v>32.8428</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.154</v>
+        <v>-0.2139000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>5.7984</v>
+        <v>2.5359</v>
       </c>
       <c r="U20" t="n">
-        <v>-6.9521</v>
+        <v>-2.7498</v>
       </c>
       <c r="V20" t="n">
         <v>-20.7819</v>
@@ -2047,13 +2047,13 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>-21.5087</v>
+        <v>-15.1129</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.490400000000001</v>
+        <v>-2.1858</v>
       </c>
       <c r="F21" t="n">
-        <v>-15.0179</v>
+        <v>-12.9269</v>
       </c>
       <c r="G21" t="n">
         <v>-15.4371</v>
@@ -2092,13 +2092,13 @@
         <v>12.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>-4.4171</v>
+        <v>1.9785</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.4428</v>
+        <v>-0.1381</v>
       </c>
       <c r="U21" t="n">
-        <v>0.02569999999999995</v>
+        <v>2.1166</v>
       </c>
       <c r="V21" t="n">
         <v>0.9554000000000002</v>
@@ -2125,13 +2125,13 @@
         <v>32</v>
       </c>
       <c r="D22" t="n">
-        <v>115.6707</v>
+        <v>149.6086000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>180.8942</v>
+        <v>190.1412</v>
       </c>
       <c r="F22" t="n">
-        <v>-65.2243</v>
+        <v>-40.5344</v>
       </c>
       <c r="G22" t="n">
         <v>124.6213</v>
@@ -2140,7 +2140,7 @@
         <v>122.557</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0649</v>
+        <v>2.064899999999993</v>
       </c>
       <c r="J22" t="n">
         <v>387.0644</v>
@@ -2170,13 +2170,13 @@
         <v>415.4334000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.849399999999998</v>
+        <v>31.0881</v>
       </c>
       <c r="T22" t="n">
-        <v>-10.8496</v>
+        <v>-1.600700000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>7.999899999999998</v>
+        <v>32.6899</v>
       </c>
       <c r="V22" t="n">
         <v>10.2111</v>
